--- a/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
@@ -21,25 +21,25 @@
     <t>Migración métrica · El esclavo del demonio</t>
   </si>
   <si>
-    <t>Para Blanca Ballester Morell · generado el 2026-09-19</t>
-  </si>
-  <si>
-    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, con este mismo texto. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
-  </si>
-  <si>
-    <t>En Responder están las preguntas que no hemos podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
-  </si>
-  <si>
-    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiremos a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
-  </si>
-  <si>
-    <t>En Confirmar aparecen las respuestas que hemos rellenado nosotros a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+    <t>Para Blanca Ballester Morell · generado el 2026-09-20</t>
+  </si>
+  <si>
+    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
+  </si>
+  <si>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+  </si>
+  <si>
+    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
+  </si>
+  <si>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
   </si>
   <si>
     <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
   </si>
   <si>
-    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntaselo a David antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y corregir allí lo que haga falta.</t>
+    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
     <t>Cuando no hay desplegable, los formatos son estos:</t>
@@ -165,7 +165,7 @@
     <t>Redondilla · Octosílaba</t>
   </si>
   <si>
-    <t>Sus 138 versos no encajan con «Octosílaba», que se compone de unidades completas de 4 versos. Encajaría con 2 versos más (140) o con 2 versos menos (136).</t>
+    <t>Sus 138 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 2 versos más (140) o con 2 versos menos (136).</t>
   </si>
   <si>
     <t>L|76cc2aa0-50c6-4ac7-a229-c158e6984144</t>
@@ -840,7 +840,7 @@
     <t>redondilla</t>
   </si>
   <si>
-    <t>Revisar: Sus 138 versos no encajan con «Octosílaba», que se compone de unidades completas de 4 versos. Encajaría con 2 versos más (140) o con 2 versos menos (136).</t>
+    <t>Revisar: Sus 138 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 2 versos más (140) o con 2 versos menos (136).</t>
   </si>
 </sst>
 </file>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="270">
   <si>
     <t>Migración métrica · El esclavo del demonio</t>
   </si>
@@ -33,10 +33,10 @@
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
   </si>
   <si>
-    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
-  </si>
-  <si>
-    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Ahí van también los tramos que vuelven a ser una sola secuencia. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+  </si>
+  <si>
+    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual, así que basta con revisarlas: la columna «¿Correcto?» tiene el mismo desplegable que la pestaña anterior y solo hay que tocarla si algo no queda como digo. La columna «Sílabas del verso» es únicamente para los versos hipométricos e hipermétricos, por si tienes a mano cuántas sílabas mide el verso; si no la rellenas, se registra que tiene menos o más de las que le tocan, sin dar una cifra. En las demás filas esa celda está apagada.</t>
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
@@ -177,15 +177,219 @@
     <t>2766–2935</t>
   </si>
   <si>
+    <t>Esquema de rima · estrofa 1 (vv. 2766–2770)</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2766</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 2 (vv. 2771–2775)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2771</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 3 (vv. 2776–2780)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2776</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 4 (vv. 2781–2785)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2781</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 5 (vv. 2786–2790)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2786</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 6 (vv. 2791–2795)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2791</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 7 (vv. 2796–2800)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2796</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 8 (vv. 2801–2805)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2801</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 9 (vv. 2806–2810)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2806</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 10 (vv. 2811–2815)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2811</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 11 (vv. 2816–2820)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2816</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 12 (vv. 2821–2825)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2821</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 13 (vv. 2826–2830)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2826</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 14 (vv. 2831–2835)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2831</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 15 (vv. 2836–2840)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2836</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 16 (vv. 2841–2845)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2841</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 17 (vv. 2846–2850)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2846</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 18 (vv. 2851–2855)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2851</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 19 (vv. 2856–2860)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2856</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 20 (vv. 2861–2865)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2861</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 21 (vv. 2866–2870)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2866</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 22 (vv. 2871–2875)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2871</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 23 (vv. 2876–2880)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2876</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 24 (vv. 2881–2885)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2881</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 25 (vv. 2886–2890)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2886</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 26 (vv. 2891–2895)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2891</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 27 (vv. 2896–2900)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2896</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 28 (vv. 2901–2905)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2901</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 29 (vv. 2906–2910)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2906</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 30 (vv. 2911–2915)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2911</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 31 (vv. 2916–2920)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2916</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 32 (vv. 2921–2925)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2921</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 33 (vv. 2926–2930)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2926</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 34 (vv. 2931–2935)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2931</t>
+  </si>
+  <si>
     <t>Esquema de rima · 34 estrofas</t>
   </si>
   <si>
     <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta)</t>
   </si>
   <si>
-    <t>R|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
-  </si>
-  <si>
     <t>R|76cc2aa0-50c6-4ac7-a229-c158e6984144|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
   </si>
   <si>
@@ -441,10 +645,10 @@
     <t>Cómo queda</t>
   </si>
   <si>
-    <t>Sílabas</t>
-  </si>
-  <si>
-    <t>Informativa</t>
+    <t>Sílabas del verso</t>
+  </si>
+  <si>
+    <t>Revisar</t>
   </si>
   <si>
     <t>Romance · Octosílabo (1649–1760)</t>
@@ -1435,7 +1639,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1582,13 +1786,13 @@
         <v>51</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>44</v>
@@ -1606,20 +1810,1079 @@
         <v>44</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G37">
+      <formula1>Listas!$B$2:$B$9</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2:G3">
       <formula1>Listas!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G38">
+      <formula1>Listas!$C$2:$C$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G37">
       <formula1>Listas!$B$2:$B$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5">
-      <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1651,19 +2914,19 @@
         <v>32</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>38</v>
@@ -1674,19 +2937,19 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>44</v>
@@ -1698,24 +2961,24 @@
         <v>44</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>44</v>
@@ -1727,24 +2990,24 @@
         <v>44</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>44</v>
@@ -1756,24 +3019,24 @@
         <v>44</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>44</v>
@@ -1785,24 +3048,24 @@
         <v>44</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>44</v>
@@ -1814,24 +3077,24 @@
         <v>44</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>44</v>
@@ -1843,24 +3106,24 @@
         <v>44</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>44</v>
@@ -1872,24 +3135,24 @@
         <v>44</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>44</v>
@@ -1901,24 +3164,24 @@
         <v>44</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>44</v>
@@ -1930,24 +3193,24 @@
         <v>44</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>44</v>
@@ -1959,24 +3222,24 @@
         <v>44</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>44</v>
@@ -1988,24 +3251,24 @@
         <v>44</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>44</v>
@@ -2017,24 +3280,24 @@
         <v>44</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>44</v>
@@ -2046,24 +3309,24 @@
         <v>44</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>107</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>44</v>
@@ -2075,24 +3338,24 @@
         <v>44</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>44</v>
@@ -2104,24 +3367,24 @@
         <v>44</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>113</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>44</v>
@@ -2133,24 +3396,24 @@
         <v>44</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>44</v>
@@ -2162,24 +3425,24 @@
         <v>44</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>118</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>44</v>
@@ -2191,24 +3454,24 @@
         <v>44</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>44</v>
@@ -2220,24 +3483,24 @@
         <v>44</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>44</v>
@@ -2249,24 +3512,24 @@
         <v>44</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>44</v>
@@ -2278,24 +3541,24 @@
         <v>44</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>44</v>
@@ -2307,7 +3570,7 @@
         <v>44</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2336,7 +3599,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
@@ -2350,22 +3613,22 @@
         <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>38</v>
@@ -2376,22 +3639,22 @@
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>145</v>
+        <v>213</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>146</v>
+        <v>214</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>44</v>
@@ -2403,11 +3666,16 @@
         <v>44</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H2">
+      <formula1>Listas!$D$2:$D$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2433,37 +3701,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>34</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2471,34 +3739,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="C2" s="3">
         <v>235</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>159</v>
+        <v>227</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2506,34 +3774,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="C3" s="3">
         <v>164</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>167</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2541,34 +3809,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>168</v>
+        <v>236</v>
       </c>
       <c r="C4" s="3">
         <v>215</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>170</v>
+        <v>238</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2576,34 +3844,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="C5" s="3">
         <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>171</v>
+        <v>239</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2617,28 +3885,28 @@
         <v>150</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>176</v>
+        <v>244</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2646,34 +3914,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="C7" s="3">
         <v>4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2681,34 +3949,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="C8" s="3">
         <v>120</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2716,34 +3984,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="C9" s="3">
         <v>164</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2751,34 +4019,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="C10" s="3">
         <v>120</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2786,34 +4054,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="C11" s="3">
         <v>210</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2821,34 +4089,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="C12" s="3">
         <v>144</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2856,34 +4124,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="C13" s="3">
         <v>14</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2891,34 +4159,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="C14" s="3">
         <v>48</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2926,34 +4194,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="C15" s="3">
         <v>34</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>171</v>
+        <v>239</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2961,34 +4229,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="C16" s="3">
         <v>112</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>167</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2996,34 +4264,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="C17" s="3">
         <v>80</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3031,34 +4299,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="C18" s="3">
         <v>37</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>171</v>
+        <v>239</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3066,34 +4334,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="C19" s="3">
         <v>124</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3101,34 +4369,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="C20" s="3">
         <v>37</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>171</v>
+        <v>239</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3136,34 +4404,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="C21" s="3">
         <v>14</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3171,34 +4439,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="C22" s="3">
         <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3206,34 +4474,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="C23" s="3">
         <v>32</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>171</v>
+        <v>239</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3241,34 +4509,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="C24" s="3">
         <v>195</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3276,34 +4544,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="C25" s="3">
         <v>152</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>167</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3311,34 +4579,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="C26" s="3">
         <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>167</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3346,34 +4614,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="C27" s="3">
         <v>14</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3387,28 +4655,28 @@
         <v>170</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3422,28 +4690,28 @@
         <v>138</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3451,34 +4719,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="C30" s="3">
         <v>58</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>171</v>
+        <v>239</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3486,34 +4754,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="C31" s="3">
         <v>164</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>167</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="266">
   <si>
     <t>Migración métrica · El esclavo del demonio</t>
   </si>
   <si>
-    <t>Para Blanca Ballester Morell · generado el 2026-09-20</t>
+    <t>Para Blanca Ballester Morell · generado el 2026-09-21</t>
   </si>
   <si>
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
@@ -66,385 +66,373 @@
     <t>Tipología 1 · ababa</t>
   </si>
   <si>
+    <t>Es correcto</t>
+  </si>
+  <si>
+    <t>El rango está mal (indico el correcto)</t>
+  </si>
+  <si>
+    <t>Tipología 2 · abbab</t>
+  </si>
+  <si>
+    <t>No es así (lo corrijo al lado)</t>
+  </si>
+  <si>
+    <t>Es otra forma (indico cuál)</t>
+  </si>
+  <si>
+    <t>Tipología 3 · abaab</t>
+  </si>
+  <si>
+    <t>Es otra cosa (lo explico al lado)</t>
+  </si>
+  <si>
+    <t>Tipología 4 · aabab</t>
+  </si>
+  <si>
+    <t>Tipología 5 · aabba</t>
+  </si>
+  <si>
+    <t>Tipología 6 · abbaa</t>
+  </si>
+  <si>
+    <t>Tipología 7 · ababb</t>
+  </si>
+  <si>
+    <t>Tipología 8 · abbba</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Versos</t>
+  </si>
+  <si>
+    <t>Forma</t>
+  </si>
+  <si>
+    <t>Qué se pregunta</t>
+  </si>
+  <si>
+    <t>Propuesta</t>
+  </si>
+  <si>
+    <t>Cómo contestar</t>
+  </si>
+  <si>
+    <t>Respuesta</t>
+  </si>
+  <si>
+    <t>Excepciones / detalle</t>
+  </si>
+  <si>
+    <t>Comentario</t>
+  </si>
+  <si>
+    <t>Clave</t>
+  </si>
+  <si>
+    <t>Decidir</t>
+  </si>
+  <si>
+    <t>641–790</t>
+  </si>
+  <si>
+    <t>Quintilla · Octosílaba consonante</t>
+  </si>
+  <si>
+    <t>El subtipo 762–765 tiene 4 versos, cuando una estrofa de esta forma tiene 5. Hay versos sin subtipo: 761. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Elige en el desplegable y explícalo al lado</t>
+  </si>
+  <si>
+    <t>L|eb604b92-57a5-415b-a148-612a0624d91d</t>
+  </si>
+  <si>
+    <t>2936–3073</t>
+  </si>
+  <si>
+    <t>Redondilla · Octosílaba</t>
+  </si>
+  <si>
+    <t>Sus 138 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 2 versos más (140) o con 2 versos menos (136). Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+  </si>
+  <si>
+    <t>L|76cc2aa0-50c6-4ac7-a229-c158e6984144</t>
+  </si>
+  <si>
+    <t>Responder</t>
+  </si>
+  <si>
+    <t>2766–2935</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 1 (vv. 2766–2770)</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2766</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 2 (vv. 2771–2775)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2771</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 3 (vv. 2776–2780)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2776</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 4 (vv. 2781–2785)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2781</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 5 (vv. 2786–2790)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2786</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 6 (vv. 2791–2795)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2791</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 7 (vv. 2796–2800)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2796</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 8 (vv. 2801–2805)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2801</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 9 (vv. 2806–2810)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2806</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 10 (vv. 2811–2815)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2811</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 11 (vv. 2816–2820)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2816</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 12 (vv. 2821–2825)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2821</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 13 (vv. 2826–2830)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2826</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 14 (vv. 2831–2835)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2831</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 15 (vv. 2836–2840)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2836</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 16 (vv. 2841–2845)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2841</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 17 (vv. 2846–2850)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2846</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 18 (vv. 2851–2855)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2851</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 19 (vv. 2856–2860)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2856</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 20 (vv. 2861–2865)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2861</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 21 (vv. 2866–2870)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2866</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 22 (vv. 2871–2875)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2871</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 23 (vv. 2876–2880)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2876</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 24 (vv. 2881–2885)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2881</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 25 (vv. 2886–2890)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2886</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 26 (vv. 2891–2895)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2891</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 27 (vv. 2896–2900)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2896</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 28 (vv. 2901–2905)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2901</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 29 (vv. 2906–2910)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2906</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 30 (vv. 2911–2915)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2911</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 31 (vv. 2916–2920)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2916</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 32 (vv. 2921–2925)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2921</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 33 (vv. 2926–2930)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2926</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 34 (vv. 2931–2935)</t>
+  </si>
+  <si>
+    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2931</t>
+  </si>
+  <si>
+    <t>Pregunta</t>
+  </si>
+  <si>
+    <t>Vocabulario anterior</t>
+  </si>
+  <si>
+    <t>¿Correcto?</t>
+  </si>
+  <si>
+    <t>Corrección</t>
+  </si>
+  <si>
+    <t>236–399</t>
+  </si>
+  <si>
+    <t>Romance · Octosílabo</t>
+  </si>
+  <si>
+    <t>Vocales de la asonancia</t>
+  </si>
+  <si>
+    <t>o-a</t>
+  </si>
+  <si>
+    <t>romance_o-a</t>
+  </si>
+  <si>
+    <t>C|bf2f64bf-da86-43ca-8943-07833f7690ff</t>
+  </si>
+  <si>
+    <t>615–640</t>
+  </si>
+  <si>
+    <t>Endecasílabo suelto · Endecasílabo</t>
+  </si>
+  <si>
+    <t>Varias respuestas</t>
+  </si>
+  <si>
+    <t>Densidad de rima: Ninguna; Dístico final: sí; Organización en pareados: Ninguna</t>
+  </si>
+  <si>
+    <t>endecasilabo_suelto_puro</t>
+  </si>
+  <si>
+    <t>C|56257c7a-29ae-46f2-85d5-ca1439a2e46e</t>
+  </si>
+  <si>
+    <t>791–794</t>
+  </si>
+  <si>
+    <t>Esquema de rima</t>
+  </si>
+  <si>
     <t>Abrazada · abba</t>
-  </si>
-  <si>
-    <t>Es correcto</t>
-  </si>
-  <si>
-    <t>El rango está mal (indico el correcto)</t>
-  </si>
-  <si>
-    <t>Tipología 2 · abbab</t>
-  </si>
-  <si>
-    <t>Cruzada · abab</t>
-  </si>
-  <si>
-    <t>No es así (lo corrijo al lado)</t>
-  </si>
-  <si>
-    <t>Es otra forma (indico cuál)</t>
-  </si>
-  <si>
-    <t>Tipología 3 · abaab</t>
-  </si>
-  <si>
-    <t>Es otra cosa (lo explico al lado)</t>
-  </si>
-  <si>
-    <t>Tipología 4 · aabab</t>
-  </si>
-  <si>
-    <t>Tipología 5 · aabba</t>
-  </si>
-  <si>
-    <t>Tipología 6 · abbaa</t>
-  </si>
-  <si>
-    <t>Tipología 7 · ababb</t>
-  </si>
-  <si>
-    <t>Tipología 8 · abbba</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Versos</t>
-  </si>
-  <si>
-    <t>Forma</t>
-  </si>
-  <si>
-    <t>Qué se pregunta</t>
-  </si>
-  <si>
-    <t>Propuesta</t>
-  </si>
-  <si>
-    <t>Cómo contestar</t>
-  </si>
-  <si>
-    <t>Respuesta</t>
-  </si>
-  <si>
-    <t>Excepciones / detalle</t>
-  </si>
-  <si>
-    <t>Comentario</t>
-  </si>
-  <si>
-    <t>Clave</t>
-  </si>
-  <si>
-    <t>Decidir</t>
-  </si>
-  <si>
-    <t>641–790</t>
-  </si>
-  <si>
-    <t>Quintilla · Octosílaba consonante</t>
-  </si>
-  <si>
-    <t>El subtipo 762–765 tiene 4 versos, cuando una estrofa de esta forma tiene 5. Hay versos sin subtipo: 761.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Elige en el desplegable y explícalo al lado</t>
-  </si>
-  <si>
-    <t>L|eb604b92-57a5-415b-a148-612a0624d91d</t>
-  </si>
-  <si>
-    <t>2936–3073</t>
-  </si>
-  <si>
-    <t>Redondilla · Octosílaba</t>
-  </si>
-  <si>
-    <t>Sus 138 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 2 versos más (140) o con 2 versos menos (136).</t>
-  </si>
-  <si>
-    <t>L|76cc2aa0-50c6-4ac7-a229-c158e6984144</t>
-  </si>
-  <si>
-    <t>Responder</t>
-  </si>
-  <si>
-    <t>2766–2935</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 1 (vv. 2766–2770)</t>
-  </si>
-  <si>
-    <t>Elige en el desplegable</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2766</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 2 (vv. 2771–2775)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2771</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 3 (vv. 2776–2780)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2776</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 4 (vv. 2781–2785)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2781</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 5 (vv. 2786–2790)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2786</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 6 (vv. 2791–2795)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2791</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 7 (vv. 2796–2800)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2796</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 8 (vv. 2801–2805)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2801</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 9 (vv. 2806–2810)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2806</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 10 (vv. 2811–2815)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2811</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 11 (vv. 2816–2820)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2816</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 12 (vv. 2821–2825)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2821</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 13 (vv. 2826–2830)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2826</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 14 (vv. 2831–2835)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2831</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 15 (vv. 2836–2840)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2836</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 16 (vv. 2841–2845)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2841</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 17 (vv. 2846–2850)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2846</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 18 (vv. 2851–2855)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2851</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 19 (vv. 2856–2860)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2856</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 20 (vv. 2861–2865)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2861</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 21 (vv. 2866–2870)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2866</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 22 (vv. 2871–2875)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2871</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 23 (vv. 2876–2880)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2876</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 24 (vv. 2881–2885)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2881</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 25 (vv. 2886–2890)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2886</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 26 (vv. 2891–2895)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2891</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 27 (vv. 2896–2900)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2896</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 28 (vv. 2901–2905)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2901</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 29 (vv. 2906–2910)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2906</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 30 (vv. 2911–2915)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2911</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 31 (vv. 2916–2920)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2916</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 32 (vv. 2921–2925)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2921</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 33 (vv. 2926–2930)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2926</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 34 (vv. 2931–2935)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2931</t>
-  </si>
-  <si>
-    <t>Esquema de rima · 34 estrofas</t>
-  </si>
-  <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta)</t>
-  </si>
-  <si>
-    <t>R|76cc2aa0-50c6-4ac7-a229-c158e6984144|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
-  </si>
-  <si>
-    <t>Pregunta</t>
-  </si>
-  <si>
-    <t>Vocabulario anterior</t>
-  </si>
-  <si>
-    <t>¿Correcto?</t>
-  </si>
-  <si>
-    <t>Corrección</t>
-  </si>
-  <si>
-    <t>236–399</t>
-  </si>
-  <si>
-    <t>Romance · Octosílabo</t>
-  </si>
-  <si>
-    <t>Vocales de la asonancia</t>
-  </si>
-  <si>
-    <t>o-a</t>
-  </si>
-  <si>
-    <t>romance_o-a</t>
-  </si>
-  <si>
-    <t>C|bf2f64bf-da86-43ca-8943-07833f7690ff</t>
-  </si>
-  <si>
-    <t>615–640</t>
-  </si>
-  <si>
-    <t>Endecasílabo suelto · Endecasílabo</t>
-  </si>
-  <si>
-    <t>Varias respuestas</t>
-  </si>
-  <si>
-    <t>Densidad de rima: Ninguna; Dístico final: sí; Organización en pareados: Ninguna</t>
-  </si>
-  <si>
-    <t>endecasilabo_suelto_puro</t>
-  </si>
-  <si>
-    <t>C|56257c7a-29ae-46f2-85d5-ca1439a2e46e</t>
-  </si>
-  <si>
-    <t>791–794</t>
-  </si>
-  <si>
-    <t>Esquema de rima</t>
   </si>
   <si>
     <t>redondilla_regular</t>
@@ -1547,13 +1535,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="40" customWidth="1"/>
+    <col min="1" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1563,11 +1551,8 @@
       <c r="C1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1577,58 +1562,52 @@
       <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1639,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1655,1231 +1634,1196 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G5" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G6" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G8" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G9" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G11" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G12" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G13" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G15" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G16" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G18" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G23" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G24" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G25" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G26" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G27" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G28" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G29" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G30" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G31" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G32" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G33" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G34" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G35" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G36" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G37" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G37">
       <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2:G3">
       <formula1>Listas!$A$2:$A$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G38">
-      <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G37">
       <formula1>Listas!$B$2:$B$9</formula1>
@@ -2908,679 +2852,679 @@
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="E5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>154</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F10:F23">
-      <formula1>Listas!$D$2:$D$3</formula1>
+      <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F2:F23">
-      <formula1>Listas!$D$2:$D$3</formula1>
+      <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3607,73 +3551,73 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>209</v>
-      </c>
       <c r="H1" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="G2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>211</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>215</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H2">
-      <formula1>Listas!$D$2:$D$3</formula1>
+      <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3701,37 +3645,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3739,34 +3683,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C2" s="3">
         <v>235</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3774,34 +3718,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3">
         <v>164</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3809,34 +3753,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C4" s="3">
         <v>215</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3844,34 +3788,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C5" s="3">
         <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3879,34 +3823,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3">
         <v>150</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3914,34 +3858,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C7" s="3">
         <v>4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3949,34 +3893,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C8" s="3">
         <v>120</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3984,34 +3928,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C9" s="3">
         <v>164</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4019,34 +3963,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C10" s="3">
         <v>120</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4054,34 +3998,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C11" s="3">
         <v>210</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4089,34 +4033,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C12" s="3">
         <v>144</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4124,34 +4068,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C13" s="3">
         <v>14</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4159,34 +4103,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C14" s="3">
         <v>48</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4194,34 +4138,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C15" s="3">
         <v>34</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4229,34 +4173,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C16" s="3">
         <v>112</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4264,34 +4208,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C17" s="3">
         <v>80</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4299,34 +4243,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C18" s="3">
         <v>37</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4334,34 +4278,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C19" s="3">
         <v>124</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4369,34 +4313,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C20" s="3">
         <v>37</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4404,34 +4348,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C21" s="3">
         <v>14</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4439,34 +4383,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C22" s="3">
         <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4474,34 +4418,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C23" s="3">
         <v>32</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4509,34 +4453,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C24" s="3">
         <v>195</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4544,34 +4488,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C25" s="3">
         <v>152</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4579,34 +4523,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C26" s="3">
         <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4614,34 +4558,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C27" s="3">
         <v>14</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4649,34 +4593,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C28" s="3">
         <v>170</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4684,34 +4628,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C29" s="3">
         <v>138</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4719,34 +4663,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C30" s="3">
         <v>58</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4754,34 +4698,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3">
         <v>164</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="270">
   <si>
     <t>Migración métrica · El esclavo del demonio</t>
   </si>
@@ -66,6 +66,9 @@
     <t>Tipología 1 · ababa</t>
   </si>
   <si>
+    <t>Abrazada · abba</t>
+  </si>
+  <si>
     <t>Es correcto</t>
   </si>
   <si>
@@ -75,6 +78,9 @@
     <t>Tipología 2 · abbab</t>
   </si>
   <si>
+    <t>Cruzada · abab</t>
+  </si>
+  <si>
     <t>No es así (lo corrijo al lado)</t>
   </si>
   <si>
@@ -141,7 +147,7 @@
     <t>Quintilla · Octosílaba consonante</t>
   </si>
   <si>
-    <t>El subtipo 762–765 tiene 4 versos, cuando una estrofa de esta forma tiene 5. Hay versos sin subtipo: 761. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>El subtipo 762–765 tiene 4 versos, cuando una estrofa de esta forma tiene 5. Hay versos sin subtipo: 761.</t>
   </si>
   <si>
     <t/>
@@ -159,7 +165,7 @@
     <t>Redondilla · Octosílaba</t>
   </si>
   <si>
-    <t>Sus 138 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 2 versos más (140) o con 2 versos menos (136). Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Sus 138 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 2 versos más (140) o con 2 versos menos (136). Lo demás que te pregunto de este pasaje va contestado de una vez para todas sus estrofas, así que la respuesta vale igual si el rango cambia.</t>
   </si>
   <si>
     <t>L|76cc2aa0-50c6-4ac7-a229-c158e6984144</t>
@@ -378,6 +384,15 @@
     <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2931</t>
   </si>
   <si>
+    <t>Esquema de rima · todas las estrofas</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta). Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+  </si>
+  <si>
+    <t>R|76cc2aa0-50c6-4ac7-a229-c158e6984144|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
+  </si>
+  <si>
     <t>Pregunta</t>
   </si>
   <si>
@@ -430,9 +445,6 @@
   </si>
   <si>
     <t>Esquema de rima</t>
-  </si>
-  <si>
-    <t>Abrazada · abba</t>
   </si>
   <si>
     <t>redondilla_regular</t>
@@ -1535,13 +1547,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="40" customWidth="1"/>
+    <col min="1" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1551,8 +1563,11 @@
       <c r="C1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1562,52 +1577,58 @@
       <c r="C2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1618,7 +1639,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1634,1196 +1655,1231 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="G3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="G5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G37">
       <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2:G3">
       <formula1>Listas!$A$2:$A$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G38">
+      <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G37">
       <formula1>Listas!$B$2:$B$9</formula1>
@@ -2852,679 +2908,679 @@
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F10:F23">
-      <formula1>Listas!$C$2:$C$3</formula1>
+      <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F2:F23">
-      <formula1>Listas!$C$2:$C$3</formula1>
+      <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3551,73 +3607,73 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H2">
-      <formula1>Listas!$C$2:$C$3</formula1>
+      <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3645,37 +3701,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3683,34 +3739,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C2" s="3">
         <v>235</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3718,34 +3774,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C3" s="3">
         <v>164</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3753,34 +3809,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C4" s="3">
         <v>215</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3788,34 +3844,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C5" s="3">
         <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3823,34 +3879,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3">
         <v>150</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3858,34 +3914,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C7" s="3">
         <v>4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3893,34 +3949,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C8" s="3">
         <v>120</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3928,34 +3984,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C9" s="3">
         <v>164</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3963,34 +4019,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C10" s="3">
         <v>120</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3998,34 +4054,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C11" s="3">
         <v>210</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4033,34 +4089,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C12" s="3">
         <v>144</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4068,34 +4124,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C13" s="3">
         <v>14</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4103,34 +4159,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C14" s="3">
         <v>48</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4138,34 +4194,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C15" s="3">
         <v>34</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4173,34 +4229,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C16" s="3">
         <v>112</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4208,34 +4264,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C17" s="3">
         <v>80</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4243,34 +4299,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C18" s="3">
         <v>37</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4278,34 +4334,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C19" s="3">
         <v>124</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4313,34 +4369,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C20" s="3">
         <v>37</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4348,34 +4404,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C21" s="3">
         <v>14</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4383,34 +4439,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C22" s="3">
         <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4418,34 +4474,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C23" s="3">
         <v>32</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4453,34 +4509,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C24" s="3">
         <v>195</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4488,34 +4544,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C25" s="3">
         <v>152</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4523,34 +4579,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C26" s="3">
         <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4558,34 +4614,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C27" s="3">
         <v>14</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4593,34 +4649,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C28" s="3">
         <v>170</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4628,34 +4684,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C29" s="3">
         <v>138</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4663,34 +4719,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C30" s="3">
         <v>58</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4698,34 +4754,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C31" s="3">
         <v>164</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="204">
   <si>
     <t>Migración métrica · El esclavo del demonio</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -54,7 +54,7 @@
     <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
   </si>
   <si>
-    <t>Excepciones: los versos de la estrofa y la respuesta que le corresponde, separando cada estrofa con punto y coma. Por ejemplo, «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -177,217 +177,19 @@
     <t>2766–2935</t>
   </si>
   <si>
-    <t>Esquema de rima · estrofa 1 (vv. 2766–2770)</t>
-  </si>
-  <si>
-    <t>Elige en el desplegable</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2766</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 2 (vv. 2771–2775)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2771</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 3 (vv. 2776–2780)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2776</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 4 (vv. 2781–2785)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2781</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 5 (vv. 2786–2790)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2786</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 6 (vv. 2791–2795)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2791</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 7 (vv. 2796–2800)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2796</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 8 (vv. 2801–2805)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2801</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 9 (vv. 2806–2810)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2806</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 10 (vv. 2811–2815)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2811</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 11 (vv. 2816–2820)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2816</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 12 (vv. 2821–2825)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2821</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 13 (vv. 2826–2830)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2826</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 14 (vv. 2831–2835)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2831</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 15 (vv. 2836–2840)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2836</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 16 (vv. 2841–2845)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2841</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 17 (vv. 2846–2850)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2846</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 18 (vv. 2851–2855)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2851</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 19 (vv. 2856–2860)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2856</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 20 (vv. 2861–2865)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2861</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 21 (vv. 2866–2870)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2866</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 22 (vv. 2871–2875)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2871</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 23 (vv. 2876–2880)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2876</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 24 (vv. 2881–2885)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2881</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 25 (vv. 2886–2890)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2886</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 26 (vv. 2891–2895)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2891</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 27 (vv. 2896–2900)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2896</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 28 (vv. 2901–2905)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2901</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 29 (vv. 2906–2910)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2906</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 30 (vv. 2911–2915)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2911</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 31 (vv. 2916–2920)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2916</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 32 (vv. 2921–2925)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2921</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 33 (vv. 2926–2930)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2926</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 34 (vv. 2931–2935)</t>
-  </si>
-  <si>
-    <t>U|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066|2931</t>
+    <t>Esquema de rima · 34 estrofas</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
+  </si>
+  <si>
+    <t>R|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
   </si>
   <si>
     <t>Esquema de rima · todas las estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta). Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
   </si>
   <si>
     <t>R|76cc2aa0-50c6-4ac7-a229-c158e6984144|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
@@ -1639,7 +1441,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1786,10 +1588,10 @@
         <v>51</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>56</v>
@@ -1798,7 +1600,7 @@
         <v>44</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>44</v>
@@ -1810,1079 +1612,20 @@
         <v>44</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G37">
-      <formula1>Listas!$B$2:$B$9</formula1>
-    </dataValidation>
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2:G3">
       <formula1>Listas!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G38">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4">
+      <formula1>Listas!$B$2:$B$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5">
       <formula1>Listas!$C$2:$C$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G37">
-      <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2914,19 +1657,19 @@
         <v>32</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>125</v>
+        <v>59</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>38</v>
@@ -2937,19 +1680,19 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>44</v>
@@ -2961,24 +1704,24 @@
         <v>44</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>44</v>
@@ -2990,24 +1733,24 @@
         <v>44</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>44</v>
@@ -3019,24 +1762,24 @@
         <v>44</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>44</v>
@@ -3048,24 +1791,24 @@
         <v>44</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>44</v>
@@ -3077,24 +1820,24 @@
         <v>44</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>44</v>
@@ -3106,24 +1849,24 @@
         <v>44</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>154</v>
+        <v>88</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>44</v>
@@ -3135,24 +1878,24 @@
         <v>44</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>158</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>44</v>
@@ -3164,24 +1907,24 @@
         <v>44</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>161</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>44</v>
@@ -3193,24 +1936,24 @@
         <v>44</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>44</v>
@@ -3222,24 +1965,24 @@
         <v>44</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>167</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>44</v>
@@ -3251,24 +1994,24 @@
         <v>44</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>171</v>
+        <v>105</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>44</v>
@@ -3280,24 +2023,24 @@
         <v>44</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>44</v>
@@ -3309,24 +2052,24 @@
         <v>44</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>175</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>44</v>
@@ -3338,24 +2081,24 @@
         <v>44</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>44</v>
@@ -3367,24 +2110,24 @@
         <v>44</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>182</v>
+        <v>116</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>44</v>
@@ -3396,24 +2139,24 @@
         <v>44</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>184</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>44</v>
@@ -3425,24 +2168,24 @@
         <v>44</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>186</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>44</v>
@@ -3454,24 +2197,24 @@
         <v>44</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>190</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>193</v>
+        <v>127</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>44</v>
@@ -3483,24 +2226,24 @@
         <v>44</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>44</v>
@@ -3512,24 +2255,24 @@
         <v>44</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>44</v>
@@ -3541,24 +2284,24 @@
         <v>44</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>200</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>202</v>
+        <v>136</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>44</v>
@@ -3570,7 +2313,7 @@
         <v>44</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>204</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -3613,22 +2356,22 @@
         <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>205</v>
+        <v>139</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>206</v>
+        <v>140</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>208</v>
+        <v>142</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>38</v>
@@ -3639,22 +2382,22 @@
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>212</v>
+        <v>146</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>214</v>
+        <v>148</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>44</v>
@@ -3666,7 +2409,7 @@
         <v>44</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>215</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3701,37 +2444,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>217</v>
+        <v>151</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>218</v>
+        <v>152</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>220</v>
+        <v>154</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>221</v>
+        <v>155</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>34</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>222</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3739,34 +2482,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>223</v>
+        <v>157</v>
       </c>
       <c r="C2" s="3">
         <v>235</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>227</v>
+        <v>161</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>230</v>
+        <v>164</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3774,34 +2517,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3">
         <v>164</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3809,34 +2552,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>236</v>
+        <v>170</v>
       </c>
       <c r="C4" s="3">
         <v>215</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>237</v>
+        <v>171</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3844,34 +2587,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="C5" s="3">
         <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>240</v>
+        <v>174</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3885,28 +2628,28 @@
         <v>150</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>243</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>244</v>
+        <v>178</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3914,34 +2657,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3">
         <v>4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3949,34 +2692,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="C8" s="3">
         <v>120</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>249</v>
+        <v>183</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3984,34 +2727,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3">
         <v>164</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>251</v>
+        <v>185</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4019,34 +2762,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3">
         <v>120</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>252</v>
+        <v>186</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4054,34 +2797,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>253</v>
+        <v>187</v>
       </c>
       <c r="C11" s="3">
         <v>210</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>254</v>
+        <v>188</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>255</v>
+        <v>189</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4089,34 +2832,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="C12" s="3">
         <v>144</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>256</v>
+        <v>190</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4124,34 +2867,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>154</v>
+        <v>88</v>
       </c>
       <c r="C13" s="3">
         <v>14</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>257</v>
+        <v>191</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>259</v>
+        <v>193</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4159,34 +2902,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="C14" s="3">
         <v>48</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4194,34 +2937,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="C15" s="3">
         <v>34</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>240</v>
+        <v>174</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4229,34 +2972,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="C16" s="3">
         <v>112</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>212</v>
+        <v>146</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4264,34 +3007,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="C17" s="3">
         <v>80</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>261</v>
+        <v>195</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4299,34 +3042,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>171</v>
+        <v>105</v>
       </c>
       <c r="C18" s="3">
         <v>37</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>240</v>
+        <v>174</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4334,34 +3077,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="C19" s="3">
         <v>124</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>262</v>
+        <v>196</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4369,34 +3112,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="C20" s="3">
         <v>37</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>240</v>
+        <v>174</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4404,34 +3147,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c r="C21" s="3">
         <v>14</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>257</v>
+        <v>191</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>259</v>
+        <v>193</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4439,34 +3182,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>182</v>
+        <v>116</v>
       </c>
       <c r="C22" s="3">
         <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>263</v>
+        <v>197</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4474,34 +3217,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="C23" s="3">
         <v>32</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>240</v>
+        <v>174</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4509,34 +3252,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>264</v>
+        <v>198</v>
       </c>
       <c r="C24" s="3">
         <v>195</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>265</v>
+        <v>199</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>266</v>
+        <v>200</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4544,34 +3287,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="C25" s="3">
         <v>152</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4579,34 +3322,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="C26" s="3">
         <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>193</v>
+        <v>127</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4614,34 +3357,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="C27" s="3">
         <v>14</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>257</v>
+        <v>191</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>259</v>
+        <v>193</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4655,28 +3398,28 @@
         <v>170</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>267</v>
+        <v>201</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4690,28 +3433,28 @@
         <v>138</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>268</v>
+        <v>202</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>269</v>
+        <v>203</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4719,34 +3462,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="C30" s="3">
         <v>58</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>240</v>
+        <v>174</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4754,34 +3497,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="C31" s="3">
         <v>164</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-esclavo-del-demonio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="199">
   <si>
     <t>Migración métrica · El esclavo del demonio</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» dice el formato y da un ejemplo.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -42,21 +42,6 @@
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
-    <t>Cuando no hay desplegable, los formatos son estos:</t>
-  </si>
-  <si>
-    <t>Medidas: el número de sílabas de cada verso, en orden y separados por espacios. Por ejemplo, «7 11 7 7 11 7 11 11».</t>
-  </si>
-  <si>
-    <t>Posiciones: en qué versos de la estrofa cae el quebrado y cuántas sílabas tiene cada uno, separados por comas. Por ejemplo, «3: 4, 8: 5» quiere decir que el verso 3 tiene cuatro sílabas y el 8 tiene cinco.</t>
-  </si>
-  <si>
-    <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
-  </si>
-  <si>
-    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
-  </si>
-  <si>
     <t>lista</t>
   </si>
   <si>
@@ -180,7 +165,7 @@
     <t>Esquema de rima · 34 estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «191-194: abab; 203-206: abab»</t>
   </si>
   <si>
     <t>R|34c5beec-8c90-49f6-9bf0-eed9b0988bbe|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
@@ -189,7 +174,7 @@
     <t>Esquema de rima · todas las estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «191-194: abab; 203-206: abab». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
   </si>
   <si>
     <t>R|76cc2aa0-50c6-4ac7-a229-c158e6984144|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
@@ -911,14 +896,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1270,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1314,31 +1298,6 @@
     <row r="9" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1357,80 +1316,80 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1455,164 +1414,164 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1649,671 +1608,671 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>39</v>
+      <c r="E1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>84</v>
+        <v>72</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>87</v>
+        <v>72</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>95</v>
+        <v>72</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>97</v>
+        <v>68</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>101</v>
+        <v>95</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>104</v>
+        <v>72</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>106</v>
+        <v>68</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>109</v>
+        <v>72</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>111</v>
+        <v>68</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>115</v>
+        <v>109</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>118</v>
+        <v>72</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>120</v>
+        <v>68</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>128</v>
+        <v>122</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>134</v>
+        <v>68</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>138</v>
+        <v>132</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2348,68 +2307,68 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>39</v>
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2442,39 +2401,39 @@
     <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2482,34 +2441,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C2" s="3">
         <v>235</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2517,34 +2476,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3">
         <v>164</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2552,34 +2511,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C4" s="3">
         <v>215</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="J4" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2587,34 +2546,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3">
         <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2622,34 +2581,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3">
         <v>150</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2657,34 +2616,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C7" s="3">
         <v>4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2692,34 +2651,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C8" s="3">
         <v>120</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="J8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2727,34 +2686,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C9" s="3">
         <v>164</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="K9" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2762,34 +2721,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C10" s="3">
         <v>120</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="K10" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2797,34 +2756,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C11" s="3">
         <v>210</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="J11" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2832,34 +2791,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C12" s="3">
         <v>144</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2867,34 +2826,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C13" s="3">
         <v>14</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2902,34 +2861,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C14" s="3">
         <v>48</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2937,34 +2896,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C15" s="3">
         <v>34</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2972,34 +2931,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C16" s="3">
         <v>112</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3007,34 +2966,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C17" s="3">
         <v>80</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3042,34 +3001,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C18" s="3">
         <v>37</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3077,34 +3036,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C19" s="3">
         <v>124</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3112,34 +3071,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C20" s="3">
         <v>37</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3147,34 +3106,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C21" s="3">
         <v>14</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3182,34 +3141,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C22" s="3">
         <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3217,34 +3176,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C23" s="3">
         <v>32</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3252,34 +3211,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C24" s="3">
         <v>195</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="J24" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3287,34 +3246,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C25" s="3">
         <v>152</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3322,34 +3281,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C26" s="3">
         <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3357,34 +3316,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C27" s="3">
         <v>14</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3392,34 +3351,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C28" s="3">
         <v>170</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3427,34 +3386,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C29" s="3">
         <v>138</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3462,34 +3421,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C30" s="3">
         <v>58</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3497,34 +3456,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C31" s="3">
         <v>164</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
